--- a/FPA_Variance_Dashboard.xlsx
+++ b/FPA_Variance_Dashboard.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\itsme\OneDrive\Desktop\EXCEL_PORTFOLIO_PROJECTS\Final_Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125A7200-B82C-4B71-AE19-FE0C57AD90B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C2729E-AB36-4FEB-A175-3E7895C303A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="462" activeTab="1" xr2:uid="{45BC8B81-0CE7-4CCD-BA95-F8448F9C063B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="350" activeTab="1" xr2:uid="{45BC8B81-0CE7-4CCD-BA95-F8448F9C063B}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,12 @@
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">Dashboard!$B$16:$B$25</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">Dashboard!$C$16:$C$25</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Dashboard!$B$16:$B$25</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Dashboard!$C$16:$C$25</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Dashboard!$B$17:$B$26</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Dashboard!$C$17:$C$26</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Dashboard!$B$16:$B$25</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Dashboard!$C$16:$C$25</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">Dashboard!$B$16:$B$25</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">Dashboard!$C$16:$C$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="22">
   <si>
     <t>Department</t>
   </si>
@@ -88,9 +92,6 @@
     <t>Lookup_Key</t>
   </si>
   <si>
-    <t>Select Month:</t>
-  </si>
-  <si>
     <t>Jan</t>
   </si>
   <si>
@@ -104,6 +105,12 @@
   </si>
   <si>
     <t>Total Actual</t>
+  </si>
+  <si>
+    <t>Select Month</t>
+  </si>
+  <si>
+    <t>Net Impact ($)</t>
   </si>
 </sst>
 </file>
@@ -165,7 +172,138 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -285,6 +423,13 @@
       </cx:txPr>
     </cx:legend>
   </cx:chart>
+  <cx:spPr>
+    <a:ln w="28575">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+    </a:ln>
+  </cx:spPr>
 </cx:chartSpace>
 </file>
 
@@ -840,16 +985,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>8283</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>11596</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>621255</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>155032</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>16565</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>182217</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>591670</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>170329</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
@@ -885,8 +1030,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4257261" y="2869096"/>
-              <a:ext cx="4870174" cy="2647121"/>
+              <a:off x="7533043" y="692914"/>
+              <a:ext cx="6111239" cy="3959768"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -917,6 +1062,49 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DA4B82FB-BE81-4AFD-B590-A7A809EDB839}" name="Table1" displayName="Table1" ref="B5:F13" totalsRowShown="0" headerRowDxfId="7">
+  <autoFilter ref="B5:F13" xr:uid="{DA4B82FB-BE81-4AFD-B590-A7A809EDB839}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{625DC8D6-B110-4BDE-9CDC-2D90CABDF208}" name="Department" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{B80FDC1D-75C0-4E9D-89F8-D82D6E9D4603}" name="Budget">
+      <calculatedColumnFormula>INDEX(Raw_Data!D:D,MATCH(B6&amp;$B$3,Raw_Data!A:A,0))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{8881E498-F504-4AAD-A605-090B630AB5B5}" name="Actual">
+      <calculatedColumnFormula>INDEX(Raw_Data!E:E,MATCH(B6&amp;$B$3,Raw_Data!A:A,0))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{95E00EC3-002F-4FB5-933E-0CFD434D2BF8}" name="Variance ($)">
+      <calculatedColumnFormula>D6-C6</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{500111B8-4EDB-4648-A57F-59F7EA356B06}" name="Variance (%)" dataDxfId="5" dataCellStyle="Percent">
+      <calculatedColumnFormula>IFERROR((D6-C6)/C6,0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{41F4FEE1-B53A-4487-A4E1-97CA2DCFDD84}" name="Table4" displayName="Table4" ref="B2:B3" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="B2:B3" xr:uid="{41F4FEE1-B53A-4487-A4E1-97CA2DCFDD84}"/>
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{2FBB7D4D-C3DE-4971-A9F8-F2E511E073BB}" name="Select Month" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8719EB6D-0904-477B-909F-A6E7EBC44398}" name="Table5" displayName="Table5" ref="B16:C26" totalsRowShown="0">
+  <autoFilter ref="B16:C26" xr:uid="{8719EB6D-0904-477B-909F-A6E7EBC44398}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{03EC111A-30D7-4084-8940-BDEC88AD5292}" name="Department" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{BB76C7D9-8EC0-4FF9-A4BD-2CCF8A9A4BA8}" name="Net Impact ($)" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleDark2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1217,17 +1405,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CBA2F99-C692-4E40-AB2F-479526CABA57}">
   <dimension ref="A1:G97"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" customWidth="1"/>
-    <col min="5" max="6" width="18.140625" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" customWidth="1"/>
+    <col min="1" max="1" width="27.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" customWidth="1"/>
+    <col min="5" max="6" width="18.109375" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1250,7 +1438,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="str">
         <f>B2&amp;TEXT(C2,"MMM")</f>
         <v>SalesJan</v>
@@ -1274,7 +1462,7 @@
         <v>-5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f t="shared" ref="A3:A66" si="0">B3&amp;TEXT(C3,"MMM")</f>
         <v>SalesFeb</v>
@@ -1298,7 +1486,7 @@
         <v>-3.5200000000000002E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f t="shared" si="0"/>
         <v>SalesMar</v>
@@ -1322,7 +1510,7 @@
         <v>4.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f t="shared" si="0"/>
         <v>SalesApr</v>
@@ -1346,7 +1534,7 @@
         <v>-1.23E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f t="shared" si="0"/>
         <v>SalesMay</v>
@@ -1370,7 +1558,7 @@
         <v>-3.7600000000000001E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f t="shared" si="0"/>
         <v>SalesJun</v>
@@ -1394,7 +1582,7 @@
         <v>2.01E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f t="shared" si="0"/>
         <v>SalesJul</v>
@@ -1418,7 +1606,7 @@
         <v>-6.4899999999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f t="shared" si="0"/>
         <v>SalesAug</v>
@@ -1442,7 +1630,7 @@
         <v>-3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f t="shared" si="0"/>
         <v>SalesSep</v>
@@ -1466,7 +1654,7 @@
         <v>-2.41E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f t="shared" si="0"/>
         <v>SalesOct</v>
@@ -1490,7 +1678,7 @@
         <v>-7.9000000000000008E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f t="shared" si="0"/>
         <v>SalesNov</v>
@@ -1514,7 +1702,7 @@
         <v>5.1299999999999998E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f t="shared" si="0"/>
         <v>SalesDec</v>
@@ -1538,7 +1726,7 @@
         <v>-5.4100000000000002E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f t="shared" si="0"/>
         <v>MarketingJan</v>
@@ -1562,7 +1750,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f t="shared" si="0"/>
         <v>MarketingFeb</v>
@@ -1586,7 +1774,7 @@
         <v>1.9800000000000002E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f t="shared" si="0"/>
         <v>MarketingMar</v>
@@ -1610,7 +1798,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f t="shared" si="0"/>
         <v>MarketingApr</v>
@@ -1634,7 +1822,7 @@
         <v>-5.8799999999999998E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f t="shared" si="0"/>
         <v>MarketingMay</v>
@@ -1658,7 +1846,7 @@
         <v>-1.9599999999999999E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f t="shared" si="0"/>
         <v>MarketingJun</v>
@@ -1682,7 +1870,7 @@
         <v>-5.7200000000000001E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f t="shared" si="0"/>
         <v>MarketingJul</v>
@@ -1706,7 +1894,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f t="shared" si="0"/>
         <v>MarketingAug</v>
@@ -1730,7 +1918,7 @@
         <v>-1.35E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f t="shared" si="0"/>
         <v>MarketingSep</v>
@@ -1754,7 +1942,7 @@
         <v>-5.2600000000000001E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f t="shared" si="0"/>
         <v>MarketingOct</v>
@@ -1778,7 +1966,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f t="shared" si="0"/>
         <v>MarketingNov</v>
@@ -1802,7 +1990,7 @@
         <v>-8.4400000000000003E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f t="shared" si="0"/>
         <v>MarketingDec</v>
@@ -1826,7 +2014,7 @@
         <v>6.1600000000000002E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f t="shared" si="0"/>
         <v>OperationsJan</v>
@@ -1850,7 +2038,7 @@
         <v>-3.9399999999999998E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f t="shared" si="0"/>
         <v>OperationsFeb</v>
@@ -1874,7 +2062,7 @@
         <v>7.7000000000000002E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f t="shared" si="0"/>
         <v>OperationsMar</v>
@@ -1898,7 +2086,7 @@
         <v>-6.4600000000000005E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f t="shared" si="0"/>
         <v>OperationsApr</v>
@@ -1922,7 +2110,7 @@
         <v>5.4399999999999997E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f t="shared" si="0"/>
         <v>OperationsMay</v>
@@ -1946,7 +2134,7 @@
         <v>-7.6600000000000001E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f t="shared" si="0"/>
         <v>OperationsJun</v>
@@ -1970,7 +2158,7 @@
         <v>8.7599999999999997E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f t="shared" si="0"/>
         <v>OperationsJul</v>
@@ -1994,7 +2182,7 @@
         <v>4.8899999999999999E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f t="shared" si="0"/>
         <v>OperationsAug</v>
@@ -2018,7 +2206,7 @@
         <v>-5.4199999999999998E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <f t="shared" si="0"/>
         <v>OperationsSep</v>
@@ -2042,7 +2230,7 @@
         <v>-8.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="str">
         <f t="shared" si="0"/>
         <v>OperationsOct</v>
@@ -2066,7 +2254,7 @@
         <v>5.6800000000000003E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="str">
         <f t="shared" si="0"/>
         <v>OperationsNov</v>
@@ -2090,7 +2278,7 @@
         <v>3.7199999999999997E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="str">
         <f t="shared" si="0"/>
         <v>OperationsDec</v>
@@ -2114,7 +2302,7 @@
         <v>4.1200000000000001E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="str">
         <f t="shared" si="0"/>
         <v>R&amp;DJan</v>
@@ -2138,7 +2326,7 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="str">
         <f t="shared" si="0"/>
         <v>R&amp;DFeb</v>
@@ -2162,7 +2350,7 @@
         <v>-6.8500000000000005E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="str">
         <f t="shared" si="0"/>
         <v>R&amp;DMar</v>
@@ -2186,7 +2374,7 @@
         <v>3.8399999999999997E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="str">
         <f t="shared" si="0"/>
         <v>R&amp;DApr</v>
@@ -2210,7 +2398,7 @@
         <v>4.6899999999999997E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="str">
         <f t="shared" si="0"/>
         <v>R&amp;DMay</v>
@@ -2234,7 +2422,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="str">
         <f t="shared" si="0"/>
         <v>R&amp;DJun</v>
@@ -2258,7 +2446,7 @@
         <v>4.8800000000000003E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="str">
         <f t="shared" si="0"/>
         <v>R&amp;DJul</v>
@@ -2282,7 +2470,7 @@
         <v>-1.1000000000000001E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="str">
         <f t="shared" si="0"/>
         <v>R&amp;DAug</v>
@@ -2306,7 +2494,7 @@
         <v>4.1000000000000003E-3</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="str">
         <f t="shared" si="0"/>
         <v>R&amp;DSep</v>
@@ -2330,7 +2518,7 @@
         <v>-1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="str">
         <f t="shared" si="0"/>
         <v>R&amp;DOct</v>
@@ -2354,7 +2542,7 @@
         <v>-8.5400000000000004E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="str">
         <f t="shared" si="0"/>
         <v>R&amp;DNov</v>
@@ -2378,7 +2566,7 @@
         <v>-7.0599999999999996E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="str">
         <f t="shared" si="0"/>
         <v>R&amp;DDec</v>
@@ -2402,7 +2590,7 @@
         <v>-8.43E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="str">
         <f t="shared" si="0"/>
         <v>HRJan</v>
@@ -2426,7 +2614,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="str">
         <f t="shared" si="0"/>
         <v>HRFeb</v>
@@ -2450,7 +2638,7 @@
         <v>6.6900000000000001E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="str">
         <f t="shared" si="0"/>
         <v>HRMar</v>
@@ -2474,7 +2662,7 @@
         <v>5.4699999999999999E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="str">
         <f t="shared" si="0"/>
         <v>HRApr</v>
@@ -2498,7 +2686,7 @@
         <v>-5.6399999999999999E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="str">
         <f t="shared" si="0"/>
         <v>HRMay</v>
@@ -2522,7 +2710,7 @@
         <v>7.0699999999999999E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="str">
         <f t="shared" si="0"/>
         <v>HRJun</v>
@@ -2546,7 +2734,7 @@
         <v>7.1000000000000004E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="str">
         <f t="shared" si="0"/>
         <v>HRJul</v>
@@ -2570,7 +2758,7 @@
         <v>5.5300000000000002E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="str">
         <f t="shared" si="0"/>
         <v>HRAug</v>
@@ -2594,7 +2782,7 @@
         <v>7.1300000000000002E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="str">
         <f t="shared" si="0"/>
         <v>HRSep</v>
@@ -2618,7 +2806,7 @@
         <v>-3.2800000000000003E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="str">
         <f t="shared" si="0"/>
         <v>HROct</v>
@@ -2642,7 +2830,7 @@
         <v>-7.0199999999999999E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="str">
         <f t="shared" si="0"/>
         <v>HRNov</v>
@@ -2666,7 +2854,7 @@
         <v>-4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="str">
         <f t="shared" si="0"/>
         <v>HRDec</v>
@@ -2690,7 +2878,7 @@
         <v>-1.3100000000000001E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="str">
         <f t="shared" si="0"/>
         <v>Customer SuccessJan</v>
@@ -2714,7 +2902,7 @@
         <v>8.2900000000000001E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="str">
         <f t="shared" si="0"/>
         <v>Customer SuccessFeb</v>
@@ -2738,7 +2926,7 @@
         <v>-4.4699999999999997E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="str">
         <f t="shared" si="0"/>
         <v>Customer SuccessMar</v>
@@ -2762,7 +2950,7 @@
         <v>-5.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="str">
         <f t="shared" si="0"/>
         <v>Customer SuccessApr</v>
@@ -2786,7 +2974,7 @@
         <v>-3.5900000000000001E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="str">
         <f t="shared" si="0"/>
         <v>Customer SuccessMay</v>
@@ -2810,7 +2998,7 @@
         <v>-3.8800000000000001E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="str">
         <f t="shared" ref="A67:A97" si="1">B67&amp;TEXT(C67,"MMM")</f>
         <v>Customer SuccessJun</v>
@@ -2834,7 +3022,7 @@
         <v>-8.3400000000000002E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="str">
         <f t="shared" si="1"/>
         <v>Customer SuccessJul</v>
@@ -2858,7 +3046,7 @@
         <v>1.9699999999999999E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="str">
         <f t="shared" si="1"/>
         <v>Customer SuccessAug</v>
@@ -2882,7 +3070,7 @@
         <v>5.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="str">
         <f t="shared" si="1"/>
         <v>Customer SuccessSep</v>
@@ -2906,7 +3094,7 @@
         <v>-8.0699999999999994E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="str">
         <f t="shared" si="1"/>
         <v>Customer SuccessOct</v>
@@ -2930,7 +3118,7 @@
         <v>-3.9800000000000002E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="str">
         <f t="shared" si="1"/>
         <v>Customer SuccessNov</v>
@@ -2954,7 +3142,7 @@
         <v>7.3499999999999996E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="str">
         <f t="shared" si="1"/>
         <v>Customer SuccessDec</v>
@@ -2978,7 +3166,7 @@
         <v>-4.6899999999999997E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="str">
         <f t="shared" si="1"/>
         <v>FinanceJan</v>
@@ -3002,7 +3190,7 @@
         <v>5.3699999999999998E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="str">
         <f t="shared" si="1"/>
         <v>FinanceFeb</v>
@@ -3026,7 +3214,7 @@
         <v>-6.2899999999999998E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="str">
         <f t="shared" si="1"/>
         <v>FinanceMar</v>
@@ -3050,7 +3238,7 @@
         <v>1.5E-3</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="str">
         <f t="shared" si="1"/>
         <v>FinanceApr</v>
@@ -3074,7 +3262,7 @@
         <v>3.5200000000000002E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="str">
         <f t="shared" si="1"/>
         <v>FinanceMay</v>
@@ -3098,7 +3286,7 @@
         <v>6.4500000000000002E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="str">
         <f t="shared" si="1"/>
         <v>FinanceJun</v>
@@ -3122,7 +3310,7 @@
         <v>-3.1300000000000001E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="str">
         <f t="shared" si="1"/>
         <v>FinanceJul</v>
@@ -3146,7 +3334,7 @@
         <v>-5.04E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="str">
         <f t="shared" si="1"/>
         <v>FinanceAug</v>
@@ -3170,7 +3358,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="str">
         <f t="shared" si="1"/>
         <v>FinanceSep</v>
@@ -3194,7 +3382,7 @@
         <v>5.57E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="str">
         <f t="shared" si="1"/>
         <v>FinanceOct</v>
@@ -3218,7 +3406,7 @@
         <v>-2.7199999999999998E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="str">
         <f t="shared" si="1"/>
         <v>FinanceNov</v>
@@ -3242,7 +3430,7 @@
         <v>-7.2700000000000001E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="str">
         <f t="shared" si="1"/>
         <v>FinanceDec</v>
@@ -3266,7 +3454,7 @@
         <v>7.9299999999999995E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="str">
         <f t="shared" si="1"/>
         <v>ITJan</v>
@@ -3290,7 +3478,7 @@
         <v>8.9300000000000004E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="str">
         <f t="shared" si="1"/>
         <v>ITFeb</v>
@@ -3314,7 +3502,7 @@
         <v>8.3799999999999999E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="str">
         <f t="shared" si="1"/>
         <v>ITMar</v>
@@ -3338,7 +3526,7 @@
         <v>1.0500000000000001E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="str">
         <f t="shared" si="1"/>
         <v>ITApr</v>
@@ -3362,7 +3550,7 @@
         <v>6.8900000000000003E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="str">
         <f t="shared" si="1"/>
         <v>ITMay</v>
@@ -3386,7 +3574,7 @@
         <v>-5.6099999999999997E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="str">
         <f t="shared" si="1"/>
         <v>ITJun</v>
@@ -3410,7 +3598,7 @@
         <v>-3.9800000000000002E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="str">
         <f t="shared" si="1"/>
         <v>ITJul</v>
@@ -3434,7 +3622,7 @@
         <v>3.61E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="str">
         <f t="shared" si="1"/>
         <v>ITAug</v>
@@ -3458,7 +3646,7 @@
         <v>6.2399999999999997E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="str">
         <f t="shared" si="1"/>
         <v>ITSep</v>
@@ -3482,7 +3670,7 @@
         <v>6.4100000000000004E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="str">
         <f t="shared" si="1"/>
         <v>ITOct</v>
@@ -3506,7 +3694,7 @@
         <v>-1.72E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="str">
         <f t="shared" si="1"/>
         <v>ITNov</v>
@@ -3530,7 +3718,7 @@
         <v>6.9800000000000001E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="str">
         <f t="shared" si="1"/>
         <v>ITDec</v>
@@ -3561,25 +3749,28 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDC14A9C-38BA-4631-84BC-ED1D9AE861F4}">
-  <dimension ref="B2:F25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:F26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="3" width="18.140625" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" customWidth="1"/>
-    <col min="7" max="8" width="18.140625" customWidth="1"/>
+    <col min="2" max="3" width="18.109375" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" customWidth="1"/>
+    <col min="6" max="6" width="18.77734375" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" customWidth="1"/>
+    <col min="8" max="8" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>0</v>
       </c>
@@ -3590,22 +3781,22 @@
         <v>3</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C6">
-        <f>INDEX(Raw_Data!D:D,MATCH(B6&amp;$C$2,Raw_Data!A:A,0))</f>
+        <f>INDEX(Raw_Data!D:D,MATCH(B6&amp;$B$3,Raw_Data!A:A,0))</f>
         <v>284101</v>
       </c>
       <c r="D6">
-        <f>INDEX(Raw_Data!E:E,MATCH(B6&amp;$C$2,Raw_Data!A:A,0))</f>
+        <f>INDEX(Raw_Data!E:E,MATCH(B6&amp;$B$3,Raw_Data!A:A,0))</f>
         <v>267910</v>
       </c>
       <c r="E6">
@@ -3617,16 +3808,16 @@
         <v>-5.6990295704696568E-2</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C7">
-        <f>INDEX(Raw_Data!D:D,MATCH(B7&amp;$C$2,Raw_Data!A:A,0))</f>
+        <f>INDEX(Raw_Data!D:D,MATCH(B7&amp;$B$3,Raw_Data!A:A,0))</f>
         <v>1310207</v>
       </c>
       <c r="D7">
-        <f>INDEX(Raw_Data!E:E,MATCH(B7&amp;$C$2,Raw_Data!A:A,0))</f>
+        <f>INDEX(Raw_Data!E:E,MATCH(B7&amp;$B$3,Raw_Data!A:A,0))</f>
         <v>1353427</v>
       </c>
       <c r="E7">
@@ -3638,16 +3829,16 @@
         <v>3.298715393827082E-2</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C8">
-        <f>INDEX(Raw_Data!D:D,MATCH(B8&amp;$C$2,Raw_Data!A:A,0))</f>
+        <f>INDEX(Raw_Data!D:D,MATCH(B8&amp;$B$3,Raw_Data!A:A,0))</f>
         <v>936211</v>
       </c>
       <c r="D8">
-        <f>INDEX(Raw_Data!E:E,MATCH(B8&amp;$C$2,Raw_Data!A:A,0))</f>
+        <f>INDEX(Raw_Data!E:E,MATCH(B8&amp;$B$3,Raw_Data!A:A,0))</f>
         <v>899294</v>
       </c>
       <c r="E8">
@@ -3659,16 +3850,16 @@
         <v>-3.9432350186015756E-2</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C9">
-        <f>INDEX(Raw_Data!D:D,MATCH(B9&amp;$C$2,Raw_Data!A:A,0))</f>
+        <f>INDEX(Raw_Data!D:D,MATCH(B9&amp;$B$3,Raw_Data!A:A,0))</f>
         <v>32179</v>
       </c>
       <c r="D9">
-        <f>INDEX(Raw_Data!E:E,MATCH(B9&amp;$C$2,Raw_Data!A:A,0))</f>
+        <f>INDEX(Raw_Data!E:E,MATCH(B9&amp;$B$3,Raw_Data!A:A,0))</f>
         <v>32018</v>
       </c>
       <c r="E9">
@@ -3680,16 +3871,16 @@
         <v>-5.0032629976071354E-3</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C10">
-        <f>INDEX(Raw_Data!D:D,MATCH(B10&amp;$C$2,Raw_Data!A:A,0))</f>
+        <f>INDEX(Raw_Data!D:D,MATCH(B10&amp;$B$3,Raw_Data!A:A,0))</f>
         <v>176168</v>
       </c>
       <c r="D10">
-        <f>INDEX(Raw_Data!E:E,MATCH(B10&amp;$C$2,Raw_Data!A:A,0))</f>
+        <f>INDEX(Raw_Data!E:E,MATCH(B10&amp;$B$3,Raw_Data!A:A,0))</f>
         <v>180398</v>
       </c>
       <c r="E10">
@@ -3701,16 +3892,16 @@
         <v>2.4011171154806776E-2</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C11">
-        <f>INDEX(Raw_Data!D:D,MATCH(B11&amp;$C$2,Raw_Data!A:A,0))</f>
+        <f>INDEX(Raw_Data!D:D,MATCH(B11&amp;$B$3,Raw_Data!A:A,0))</f>
         <v>1363</v>
       </c>
       <c r="D11">
-        <f>INDEX(Raw_Data!E:E,MATCH(B11&amp;$C$2,Raw_Data!A:A,0))</f>
+        <f>INDEX(Raw_Data!E:E,MATCH(B11&amp;$B$3,Raw_Data!A:A,0))</f>
         <v>1476</v>
       </c>
       <c r="E11">
@@ -3722,16 +3913,16 @@
         <v>8.2905355832721933E-2</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C12">
-        <f>INDEX(Raw_Data!D:D,MATCH(B12&amp;$C$2,Raw_Data!A:A,0))</f>
+        <f>INDEX(Raw_Data!D:D,MATCH(B12&amp;$B$3,Raw_Data!A:A,0))</f>
         <v>204546</v>
       </c>
       <c r="D12">
-        <f>INDEX(Raw_Data!E:E,MATCH(B12&amp;$C$2,Raw_Data!A:A,0))</f>
+        <f>INDEX(Raw_Data!E:E,MATCH(B12&amp;$B$3,Raw_Data!A:A,0))</f>
         <v>215530</v>
       </c>
       <c r="E12">
@@ -3743,16 +3934,16 @@
         <v>5.3699412357122604E-2</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C13">
-        <f>INDEX(Raw_Data!D:D,MATCH(B13&amp;$C$2,Raw_Data!A:A,0))</f>
+        <f>INDEX(Raw_Data!D:D,MATCH(B13&amp;$B$3,Raw_Data!A:A,0))</f>
         <v>107335</v>
       </c>
       <c r="D13">
-        <f>INDEX(Raw_Data!E:E,MATCH(B13&amp;$C$2,Raw_Data!A:A,0))</f>
+        <f>INDEX(Raw_Data!E:E,MATCH(B13&amp;$B$3,Raw_Data!A:A,0))</f>
         <v>116922</v>
       </c>
       <c r="E13">
@@ -3764,111 +3955,124 @@
         <v>8.931848884334094E-2</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="2">
         <f>SUM(C6:C13)</f>
         <v>3052110</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="2" t="s">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C17">
+      <c r="C18" s="2">
         <f>E6</f>
         <v>-16191</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C18">
-        <f t="shared" ref="C18:C24" si="2">E7</f>
+      <c r="C19" s="2">
+        <f>E7</f>
         <v>43220</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="2" t="s">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C19">
-        <f t="shared" si="2"/>
+      <c r="C20" s="2">
+        <f>E8</f>
         <v>-36917</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="2" t="s">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C20">
-        <f t="shared" si="2"/>
+      <c r="C21" s="2">
+        <f>E9</f>
         <v>-161</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="2" t="s">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C21">
-        <f t="shared" si="2"/>
+      <c r="C22" s="2">
+        <f>E10</f>
         <v>4230</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="2" t="s">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B23" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C22">
-        <f t="shared" si="2"/>
+      <c r="C23" s="2">
+        <f>E11</f>
         <v>113</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="2" t="s">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B24" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C23">
-        <f t="shared" si="2"/>
+      <c r="C24" s="2">
+        <f>E12</f>
         <v>10984</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="2" t="s">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C24">
-        <f t="shared" si="2"/>
+      <c r="C25" s="2">
+        <f>E13</f>
         <v>9587</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="2">
         <f>SUM(D6:D13)</f>
         <v>3066975</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F6:F13">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2" xr:uid="{CDC1A7E0-CA6F-4F4D-A45E-A70F19990BB0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{CDC1A7E0-CA6F-4F4D-A45E-A70F19990BB0}">
       <formula1>"Jan, Feb, Mar, Apr, May, Jun, Jul, Aug, Sep, Oct, Nov, Dec"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <tableParts count="3">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+  </tableParts>
 </worksheet>
 </file>